--- a/Documentation/plan.xlsx
+++ b/Documentation/plan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Main_for_all\Python_Projects\MathUp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Main_for_all\Python_Projects\MathUp\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2254C76-82DF-49DA-8B14-9CA73D4D337B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D1CD38-D026-4B2F-A025-9046C2112DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="63">
   <si>
     <t>מספר משימה</t>
   </si>
@@ -126,9 +126,6 @@
     <t>יצירת תיקיות בפרויקט</t>
   </si>
   <si>
-    <t>צור תיקיות נפרדות עבור - צלילים, גרפיקה, קוד</t>
-  </si>
-  <si>
     <t>בוצע</t>
   </si>
   <si>
@@ -138,31 +135,12 @@
     <t>תיקיות בפרויקט</t>
   </si>
   <si>
-    <t>יצירת קבצים בתיקיית "code": צור קובץ ראשי, קובץ הגדרות, קובץ חלון ראשון</t>
-  </si>
-  <si>
     <t>בקוד</t>
   </si>
   <si>
-    <t>Нет</t>
-  </si>
-  <si>
     <t>בקוד ובתיקיות בפרויקט</t>
   </si>
   <si>
-    <t>מצא או צור: צבעי משחק, טקסטורות משחק, מראה דמות. הוסף משתנים קבועים לקובץ ההגדרות.
-ארגן תיקיות עם גרפיקה וצלילים.</t>
-  </si>
-  <si>
-    <t>יצירת לולאת המשחק הראשית בקובץ הקוד הראשי.</t>
-  </si>
-  <si>
-    <t>יצירת מחלקות לשימוש עתידי: Tile, MovingTile, Button, ImageButton, SelectButton, Text, MovingText.</t>
-  </si>
-  <si>
-    <t>יצירת חלון שיקבל את פני המשתמש, עליו יהיו קישוטים ואפשרויות: בחירת קושי ומהירות המשחק, הדלקה וכיבוי של הסאונד, התחל את המשחק, צא.</t>
-  </si>
-  <si>
     <t>לולאת המשחק - main.py</t>
   </si>
   <si>
@@ -178,56 +156,72 @@
     <t>מצא את כל מה שאתה צריך עבור המראה של המשחק -  settings.py, graphics, sounds</t>
   </si>
   <si>
-    <t>Описание классов</t>
-  </si>
-  <si>
     <t>יצירת המשחק עצמו עבור המשתמש - window_level.py</t>
   </si>
   <si>
-    <t>צור את הבסיס למשחק שבו ייצרו פלטפורמות ושאלות, גרם להם לזוז למטה, וצור משטח שיגור.  בעזרת מחלקות שכבר נוצרו קודם לכן</t>
-  </si>
-  <si>
     <t>יצירת מחלקת שחקן - class_player.py</t>
   </si>
   <si>
-    <t>צור מחלקת שחקן שתהיה לו יכולת לזוז ולקפוץ, שתושפע מכוח הכבידה, ושתהיה לו התנגשות עם קירות ופלטפורמות.
+    <t>הוסף שחקן למסך</t>
+  </si>
+  <si>
+    <t>השקת משחק מלא ובדיקות</t>
+  </si>
+  <si>
+    <t>מה ניתן לשפר?</t>
+  </si>
+  <si>
+    <t>בקוד - class_player.py</t>
+  </si>
+  <si>
+    <t>בקוד - window_level.py</t>
+  </si>
+  <si>
+    <t>בקוד - window_menu.py</t>
+  </si>
+  <si>
+    <t>בקוד - class_button.py ,class_text.py, class_tile.py</t>
+  </si>
+  <si>
+    <t>בקוד - main.py</t>
+  </si>
+  <si>
+    <t>בתיקיה של code</t>
+  </si>
+  <si>
+    <t>ליצור תיקיות נפרדות עבור - צלילים, גרפיקה, קוד</t>
+  </si>
+  <si>
+    <t>ליצור קבצים בתיקיית "code": לצור קובץ ראשי, קובץ הגדרות, קובץ חלון ראשון</t>
+  </si>
+  <si>
+    <t>למצא או לצור: צבעי משחק, טקסטורות משחק, מראה דמות. להוסף משתנים קבועים לקובץ ההגדרות.
+לארגן תיקיות עם גרפיקה וצלילים.</t>
+  </si>
+  <si>
+    <t>ליצור לולאת המשחק הראשית בקובץ הקוד הראשי.</t>
+  </si>
+  <si>
+    <t>ליצור מחלקות לשימוש עתידי: Tile, MovingTile, Button, ImageButton, SelectButton, Text, MovingText.</t>
+  </si>
+  <si>
+    <t>ליצור חלון שיקבל את פני המשתמש, עליו יהיו קישוטים ואפשרויות: בחירת קושי ומהירות המשחק, הדלקה וכיבוי של הסאונד, התחל את המשחק, צא.</t>
+  </si>
+  <si>
+    <t>ליצור את הבסיס למשחק שבו יוצרו פלטפורמות ושאלות, ליגרם להם לזוז למטה, וליצור משטח שיגור.  בעזרת מחלקות שכבר נוצרו קודם לכן</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ליצור מחלקת שחקן שתהיה לו יכולת לזוז ולקפוץ, שתושפע מכוח הכבידה, ושתהיה לו התנגשות עם קירות ופלטפורמות.
 שחקן ישלט באמצעות המקלדת של המשתמש.</t>
   </si>
   <si>
-    <t>הוסף שחקן למסך</t>
-  </si>
-  <si>
-    <t>הוספת שחקן למגרש המשחקים, יצירת המשחק הראשי, בדיקת התשובה הנכונה, הוספת חיים וציון שחקן. הוסף מוות של שחקן ויכולת להתחיל מחדש</t>
-  </si>
-  <si>
-    <t>השקת משחק מלא ובדיקות</t>
-  </si>
-  <si>
-    <t>השקות ובדיקות של המשחק, בדקו את תחושת המשחק ותקנו את מה שנראה מיותר או הוסיפו את מה שלטעמנו נחוץ לחוויה טובה יותר. תן לאנשים אחרים לנסות את המשחק שלנו ולקבל את דעתם כדי לתקן או להוסיף משהו.</t>
-  </si>
-  <si>
-    <t>מה ניתן לשפר?</t>
-  </si>
-  <si>
-    <t>נסו לחשוב מה אתם יכולים להוסיף אולי לאחר סיום הפרויקט יהיו לאנשים רעיונות נוספים. תחשוב גם איך אתה יכול לשפר את הפרודוקטיביות של המשחק ולפשט את הקוד.</t>
-  </si>
-  <si>
-    <t>בקוד - class_player.py</t>
-  </si>
-  <si>
-    <t>בקוד - window_level.py</t>
-  </si>
-  <si>
-    <t>בקוד - window_menu.py</t>
-  </si>
-  <si>
-    <t>בקוד - class_button.py ,class_text.py, class_tile.py</t>
-  </si>
-  <si>
-    <t>בקוד - main.py</t>
-  </si>
-  <si>
-    <t>בתיקיה של code</t>
+    <t>הוספת שחקן למגרש המשחקים, יצירת המשחק הראשי, בדיקת התשובה הנכונה, הוספת חיים וניקוד. להוסיף מוות של שחקן ויכולת להתחיל מחדש</t>
+  </si>
+  <si>
+    <t>השקות ובדיקות של המשחק, לבדקו את תחושת המשחק ולתקנו את מה שנראה מיותר או להוסיפו את מה שלטעמנו נחוץ לחוויה טובה יותר. לתת לאנשים אחרים לנסות את המשחק שלנו ולקבל את דעתם כדי לתקן או להוסיף משהו.</t>
+  </si>
+  <si>
+    <t>לנסות לחשוב מה אתם יכולים להוסיף אולי לאחר סיום הפרויקט יהיו לאנשים רעיונות נוספים. תחשוב גם איך אתה יכול לשפר את הפרודוקטיביות של המשחק ולפשט את הקוד.</t>
   </si>
 </sst>
 </file>
@@ -607,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.42578125" customWidth="1"/>
@@ -615,7 +609,7 @@
     <col min="7" max="7" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -641,7 +635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -655,17 +649,17 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -679,14 +673,14 @@
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -700,16 +694,16 @@
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="81.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="81.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -723,16 +717,16 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -746,19 +740,16 @@
         <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:8" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -772,16 +763,16 @@
         <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -795,16 +786,16 @@
         <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -812,180 +803,180 @@
         <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:8" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:8" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -993,22 +984,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="78" thickBot="1" x14ac:dyDescent="0.3">
@@ -1016,19 +1007,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18" s="2"/>
     </row>
@@ -1037,19 +1028,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G19" s="2"/>
     </row>
